--- a/Templates/Tables/SaleInfo/ProductSaleInfoTable.xlsx
+++ b/Templates/Tables/SaleInfo/ProductSaleInfoTable.xlsx
@@ -421,11 +421,17 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="2" width="12.63"/>
+    <col customWidth="1" min="1" max="1" width="10.13"/>
+    <col customWidth="1" min="2" max="2" width="7.13"/>
     <col customWidth="1" min="3" max="3" width="22.63"/>
-    <col customWidth="1" min="4" max="5" width="12.63"/>
+    <col customWidth="1" min="4" max="4" width="4.75"/>
+    <col customWidth="1" min="5" max="5" width="2.63"/>
     <col customWidth="1" min="6" max="6" width="14.25"/>
-    <col customWidth="1" min="7" max="10" width="12.63"/>
+    <col customWidth="1" min="7" max="7" width="11.75"/>
+    <col customWidth="1" min="8" max="8" width="7.63"/>
+    <col customWidth="1" min="9" max="9" width="11.25"/>
+    <col customWidth="1" min="10" max="10" width="11.38"/>
+    <col customWidth="1" min="11" max="26" width="12.63"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9794,11 +9800,17 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="2" width="12.63"/>
+    <col customWidth="1" min="1" max="1" width="9.38"/>
+    <col customWidth="1" min="2" max="2" width="7.13"/>
     <col customWidth="1" min="3" max="3" width="19.88"/>
-    <col customWidth="1" min="4" max="5" width="12.63"/>
+    <col customWidth="1" min="4" max="4" width="4.75"/>
+    <col customWidth="1" min="5" max="5" width="2.63"/>
     <col customWidth="1" min="6" max="6" width="14.25"/>
-    <col customWidth="1" min="7" max="10" width="12.63"/>
+    <col customWidth="1" min="7" max="7" width="11.75"/>
+    <col customWidth="1" min="8" max="8" width="7.63"/>
+    <col customWidth="1" min="9" max="9" width="11.25"/>
+    <col customWidth="1" min="10" max="10" width="11.38"/>
+    <col customWidth="1" min="11" max="26" width="12.63"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/Templates/Tables/SaleInfo/ProductSaleInfoTable.xlsx
+++ b/Templates/Tables/SaleInfo/ProductSaleInfoTable.xlsx
@@ -28671,15 +28671,15 @@
         <v>0.0</v>
       </c>
       <c r="K2" s="16">
-        <f>($B2*README!$C$2)+($C2*README!$C$3)+($D2*README!$C$4)+($E2*README!$C$5)+($F2*README!$C$6)</f>
+        <f>IF($A2="", -1, ($B2*README!$C$2)+($C2*README!$C$3)+($D2*README!$C$4)+($E2*README!$C$5)+($F2*README!$C$6))</f>
         <v>0</v>
       </c>
       <c r="L2" s="16">
-        <f>($B2*README!$C$2)+($C2*README!$C$3)+($D2*README!$C$4)+($E2*README!$C$5)+($F2*README!$C$6)-1</f>
+        <f>IF($A2="", -1, ($B2*README!$C$2)+($C2*README!$C$3)+($D2*README!$C$4)+($E2*README!$C$5)+($F2*README!$C$6)-1)</f>
         <v>-1</v>
       </c>
       <c r="M2" s="16">
-        <f>($B2*README!$C$2)+($C2*README!$C$3)+($D2*README!$C$4)+($E2*README!$C$5)+($F2*README!$C$6)+1</f>
+        <f>IF($A2="", -1, ($B2*README!$C$2)+($C2*README!$C$3)+($D2*README!$C$4)+($E2*README!$C$5)+($F2*README!$C$6)+1)</f>
         <v>1</v>
       </c>
       <c r="N2" s="15">
@@ -28739,15 +28739,15 @@
         <v>1.0</v>
       </c>
       <c r="K3" s="16">
-        <f>($B3*README!$C$2)+($C3*README!$C$3)+($D3*README!$C$4)+($E3*README!$C$5)+($F3*README!$C$6)</f>
+        <f>IF($A3="", -1, ($B3*README!$C$2)+($C3*README!$C$3)+($D3*README!$C$4)+($E3*README!$C$5)+($F3*README!$C$6))</f>
         <v>100</v>
       </c>
       <c r="L3" s="16">
-        <f>($B3*README!$C$2)+($C3*README!$C$3)+($D3*README!$C$4)+($E3*README!$C$5)+($F3*README!$C$6)-1</f>
+        <f>IF($A3="", -1, ($B3*README!$C$2)+($C3*README!$C$3)+($D3*README!$C$4)+($E3*README!$C$5)+($F3*README!$C$6)-1)</f>
         <v>99</v>
       </c>
       <c r="M3" s="16">
-        <f>($B3*README!$C$2)+($C3*README!$C$3)+($D3*README!$C$4)+($E3*README!$C$5)+($F3*README!$C$6)+1</f>
+        <f>IF($A3="", -1, ($B3*README!$C$2)+($C3*README!$C$3)+($D3*README!$C$4)+($E3*README!$C$5)+($F3*README!$C$6)+1)</f>
         <v>101</v>
       </c>
       <c r="N3" s="15">
@@ -28807,15 +28807,15 @@
         <v>2.0</v>
       </c>
       <c r="K4" s="16">
-        <f>($B4*README!$C$2)+($C4*README!$C$3)+($D4*README!$C$4)+($E4*README!$C$5)+($F4*README!$C$6)</f>
+        <f>IF($A4="", -1, ($B4*README!$C$2)+($C4*README!$C$3)+($D4*README!$C$4)+($E4*README!$C$5)+($F4*README!$C$6))</f>
         <v>200</v>
       </c>
       <c r="L4" s="16">
-        <f>($B4*README!$C$2)+($C4*README!$C$3)+($D4*README!$C$4)+($E4*README!$C$5)+($F4*README!$C$6)-1</f>
+        <f>IF($A4="", -1, ($B4*README!$C$2)+($C4*README!$C$3)+($D4*README!$C$4)+($E4*README!$C$5)+($F4*README!$C$6)-1)</f>
         <v>199</v>
       </c>
       <c r="M4" s="16">
-        <f>($B4*README!$C$2)+($C4*README!$C$3)+($D4*README!$C$4)+($E4*README!$C$5)+($F4*README!$C$6)+1</f>
+        <f>IF($A4="", -1, ($B4*README!$C$2)+($C4*README!$C$3)+($D4*README!$C$4)+($E4*README!$C$5)+($F4*README!$C$6)+1)</f>
         <v>201</v>
       </c>
       <c r="N4" s="15">
@@ -43123,15 +43123,15 @@
         <v>3.0</v>
       </c>
       <c r="K2" s="16">
-        <f>($B2*README!$C$2)+($C2*README!$C$3)+($D2*README!$C$4)+($E2*README!$C$5)+($F2*README!$C$6)</f>
+        <f>IF($A2="", -1, ($B2*README!$C$2)+($C2*README!$C$3)+($D2*README!$C$4)+($E2*README!$C$5)+($F2*README!$C$6))</f>
         <v>100000000</v>
       </c>
       <c r="L2" s="16">
-        <f>($B2*README!$C$2)+($C2*README!$C$3)+($D2*README!$C$4)+($E2*README!$C$5)+($F2*README!$C$6)-1</f>
+        <f>IF($A2="", -1, ($B2*README!$C$2)+($C2*README!$C$3)+($D2*README!$C$4)+($E2*README!$C$5)+($F2*README!$C$6)-1)</f>
         <v>99999999</v>
       </c>
       <c r="M2" s="16">
-        <f>($B2*README!$C$2)+($C2*README!$C$3)+($D2*README!$C$4)+($E2*README!$C$5)+($F2*README!$C$6)+1</f>
+        <f>IF($A2="", -1, ($B2*README!$C$2)+($C2*README!$C$3)+($D2*README!$C$4)+($E2*README!$C$5)+($F2*README!$C$6)+1)</f>
         <v>100000001</v>
       </c>
       <c r="N2" s="15">
@@ -43193,15 +43193,15 @@
         <v>4.0</v>
       </c>
       <c r="K3" s="16">
-        <f>($B3*README!$C$2)+($C3*README!$C$3)+($D3*README!$C$4)+($E3*README!$C$5)+($F3*README!$C$6)</f>
+        <f>IF($A3="", -1, ($B3*README!$C$2)+($C3*README!$C$3)+($D3*README!$C$4)+($E3*README!$C$5)+($F3*README!$C$6))</f>
         <v>100100000</v>
       </c>
       <c r="L3" s="16">
-        <f>($B3*README!$C$2)+($C3*README!$C$3)+($D3*README!$C$4)+($E3*README!$C$5)+($F3*README!$C$6)-1</f>
+        <f>IF($A3="", -1, ($B3*README!$C$2)+($C3*README!$C$3)+($D3*README!$C$4)+($E3*README!$C$5)+($F3*README!$C$6)-1)</f>
         <v>100099999</v>
       </c>
       <c r="M3" s="16">
-        <f>($B3*README!$C$2)+($C3*README!$C$3)+($D3*README!$C$4)+($E3*README!$C$5)+($F3*README!$C$6)+1</f>
+        <f>IF($A3="", -1, ($B3*README!$C$2)+($C3*README!$C$3)+($D3*README!$C$4)+($E3*README!$C$5)+($F3*README!$C$6)+1)</f>
         <v>100100001</v>
       </c>
       <c r="N3" s="15">

--- a/Templates/Tables/SaleInfo/ProductSaleInfoTable.xlsx
+++ b/Templates/Tables/SaleInfo/ProductSaleInfoTable.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="48">
   <si>
     <t>식별자 범위</t>
   </si>
@@ -58,6 +58,21 @@
   </si>
   <si>
     <t>대분류(11) + 중분류(10) + 소분류(100) + 베리에이션(21) =&gt; 1,101,010,021</t>
+  </si>
+  <si>
+    <t>가격 타입</t>
+  </si>
+  <si>
+    <t>광고</t>
+  </si>
+  <si>
+    <t>결제</t>
+  </si>
+  <si>
+    <t>아이템</t>
+  </si>
+  <si>
+    <t>스킬</t>
   </si>
   <si>
     <t>Description</t>
@@ -881,7 +896,9 @@
       <c r="Z13" s="1"/>
     </row>
     <row r="14">
-      <c r="A14" s="1"/>
+      <c r="A14" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
@@ -909,8 +926,12 @@
       <c r="Z14" s="1"/>
     </row>
     <row r="15">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
+      <c r="A15" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="3">
+        <v>0.0</v>
+      </c>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
@@ -937,8 +958,12 @@
       <c r="Z15" s="1"/>
     </row>
     <row r="16">
-      <c r="A16" s="1"/>
-      <c r="B16" s="1"/>
+      <c r="A16" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" s="3">
+        <v>1.0</v>
+      </c>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
@@ -965,8 +990,12 @@
       <c r="Z16" s="1"/>
     </row>
     <row r="17">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
+      <c r="A17" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17" s="3">
+        <v>2.0</v>
+      </c>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
@@ -993,8 +1022,12 @@
       <c r="Z17" s="1"/>
     </row>
     <row r="18">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
+      <c r="A18" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18" s="3">
+        <v>3.0</v>
+      </c>
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
@@ -28550,58 +28583,58 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J1" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="K1" s="6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="L1" s="7" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="M1" s="7" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="P1" s="8" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="Q1" s="9" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="R1" s="9" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="S1" s="4"/>
       <c r="T1" s="4"/>
@@ -28620,7 +28653,7 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="B2" s="10">
         <v>0.0</v>
@@ -28641,7 +28674,7 @@
         <v>0.0</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I2" s="4"/>
       <c r="J2" s="11">
@@ -28691,7 +28724,7 @@
     </row>
     <row r="3">
       <c r="A3" s="4" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="B3" s="10">
         <v>0.0</v>
@@ -28712,7 +28745,7 @@
         <v>0.0</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I3" s="4"/>
       <c r="J3" s="11">
@@ -28762,7 +28795,7 @@
     </row>
     <row r="4">
       <c r="A4" s="4" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B4" s="10">
         <v>0.0</v>
@@ -28783,7 +28816,7 @@
         <v>0.0</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I4" s="4"/>
       <c r="J4" s="17">
@@ -45569,58 +45602,58 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J1" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="K1" s="6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="L1" s="7" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="M1" s="7" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="P1" s="8" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="Q1" s="9" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="R1" s="9" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="S1" s="4"/>
       <c r="T1" s="4"/>
@@ -45641,7 +45674,7 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B2" s="15">
         <v>1.0</v>
@@ -45662,7 +45695,7 @@
         <v>0.0</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I2" s="4"/>
       <c r="J2" s="19">
@@ -45714,7 +45747,7 @@
     </row>
     <row r="3">
       <c r="A3" s="4" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B3" s="15">
         <v>1.0</v>
@@ -45735,7 +45768,7 @@
         <v>0.0</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="I3" s="4"/>
       <c r="J3" s="19">
